--- a/volunteer_application_forms/035_therapist_volunteer_application_form--volunteer_application_forms.xlsx
+++ b/volunteer_application_forms/035_therapist_volunteer_application_form--volunteer_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'abc_organization'}</t>
+          <t>abc_organization</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'ABC Organization'}</t>
+          <t>ABC Organization</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'def_organization'}</t>
+          <t>def_organization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'DEF Organization'}</t>
+          <t>DEF Organization</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'ghi_organization'}</t>
+          <t>ghi_organization</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'GHI Organization'}</t>
+          <t>GHI Organization</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2003,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2003, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2004,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2004, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2005,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2005, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2006,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2006, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2007,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2007, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3001,_'label':_'clinical_volunteer'}</t>
+          <t>clinical_volunteer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3001, 'label': 'Clinical Volunteer'}</t>
+          <t>Clinical Volunteer</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3002,_'label':_'non-clinical_volunteer'}</t>
+          <t>non-clinical_volunteer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3002, 'label': 'Non-Clinical Volunteer'}</t>
+          <t>Non-Clinical Volunteer</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3003,_'label':_'both_clinical_and_non-clinical_volunteer'}</t>
+          <t>both_clinical_and_non-clinical_volunteer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3003, 'label': 'Both Clinical and Non-Clinical Volunteer'}</t>
+          <t>Both Clinical and Non-Clinical Volunteer</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4001,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4001, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4002,_'label':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4002, 'label': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4003,_'label':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4003, 'label': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4004,_'label':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4004, 'label': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4005,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4005, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5001,_'label':_'month'}</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5001, 'label': 'Month'}</t>
+          <t>Month</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5002,_'label':_'three_months'}</t>
+          <t>three_months</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5002, 'label': 'Three Months'}</t>
+          <t>Three Months</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5003,_'label':_'six_months'}</t>
+          <t>six_months</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5003, 'label': 'Six Months'}</t>
+          <t>Six Months</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5004,_'label':_'year'}</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5004, 'label': 'Year'}</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_6001,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 6001, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_6002,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 6002, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_6003,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 6003, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_6004,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 6004, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_6005,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 6005, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_6006,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 6006, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_6007,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 6007, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_7001,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 7001, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_7002,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 7002, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
